--- a/deliverables/GPT56_SOL_SECTION32_MULTI_TRACT_SPRINT_20260716/GPT56_SOL_SECTION32_TITLE_WI_PATCH_20260716.xlsx
+++ b/deliverables/GPT56_SOL_SECTION32_MULTI_TRACT_SPRINT_20260716/GPT56_SOL_SECTION32_TITLE_WI_PATCH_20260716.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Title'!$A$1:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'WI Historical'!$A$1:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'WI Present Candidates'!$A$1:$L$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Addresses'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'WI Present Candidates'!$A$1:$L$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Addresses'!$A$1:$G$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,8 +455,8 @@
     <col width="42" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="42" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
@@ -594,12 +594,20 @@
           <t>264/345; 352/719; 352/721; 376/369</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>1/8 at 264/345; 3/16 at later original faces</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5 years by reviewed faces; commencement varies</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Direct images + schedule references</t>
+          <t>Direct original images + recorded exhibits</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -609,7 +617,7 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>Complete downstream fee/mineral and lease chains</t>
+          <t>Complete downstream fee/mineral, amendment, release, and HBP chains</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
@@ -652,12 +660,20 @@
           <t>63/33</t>
         </is>
       </c>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>1/8</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>10 years from 1947-11-13</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Direct image/assignment recital</t>
+          <t>Direct original image + recorded assignments</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -667,7 +683,7 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>Pull original OGL, releases, payout and successors</t>
+          <t>Pull amendments, releases, payout, successors, and HBP evidence</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -751,7 +767,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Eleven historic lease references</t>
+          <t>Eleven original OGL faces reviewed</t>
         </is>
       </c>
       <c r="H5" s="2" t="n"/>
@@ -762,12 +778,20 @@
           <t>Bk 872/Pg 279 schedule</t>
         </is>
       </c>
-      <c r="L5" s="2" t="n"/>
-      <c r="M5" s="2" t="n"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1/8 or 3/16 by original face; later Union ORRIs are assignment-scoped</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5 or 10 years by original face</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Partial direct-image instrument</t>
+          <t>Direct original images + assignment/exhibits</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -777,12 +801,12 @@
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>Pull complete assignment, agreement, OGLs, releases and HBP</t>
+          <t>Pull missing assignment pages, agreement, amendments, releases and HBP</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>Historic lease identities and assignment depth limitations are supported. Unique acreage, uncovered gaps, current lease status, and current quantum are NOT DETERMINED.</t>
+          <t>Original faces for all 11 listed leases and Bk 872/Pg 279 assignment/exhibits support the historic lease package and document-location math. Current lease status, HBP, successor title, and current quantum are NOT DETERMINED.</t>
         </is>
       </c>
     </row>
@@ -1393,10 +1417,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1475,7 +1499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5 / exact tract allocation open</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -1510,160 +1534,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>T2</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Diversified Production LLC — schedule-dependent claimant only</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>OK48147.001.1</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>2395/462; 2400/566</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Obtain operative schedules and predecessor title</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Diversified Production LLC — schedule-dependent claimant only</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>OK48147.001.1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2395/462; 2400/566</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Obtain operative schedules and predecessor title</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Diversified Production LLC — schedule-dependent claimant only</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>OK48147.001.1</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2395/462; 2400/566</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Obtain operative schedules and predecessor title</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Diversified Production LLC — schedule-dependent claimant only</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>OK48147.001.1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>NOT DETERMINED</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2395/462; 2400/566</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Obtain operative schedules and predecessor title</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L6"/>
+  <autoFilter ref="A1:L2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1674,10 +1546,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
@@ -1760,8 +1632,526 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Cora B. Garrett; S.A. Garrett</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Mayfield, Oklahoma</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Mayfield, OK</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Lessor locality</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>OGL 63/33 / Image 0353</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1947-11-13</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Charlie B. Crook; Ima Pearl Crook</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Route 1, Mayfield, Oklahoma</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Route 1, Mayfield, OK</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Lessor address</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>OGL 264/345 / Image 1197</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1972-02-05</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Cora B. LeGrand</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Sweetwater, Oklahoma</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Sweetwater, OK</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Lessor locality</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>OGL 307/31 / Image 1372</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1976-04-29</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>LaFortune co-trustees</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2300 Fourth National Bank Building, Tulsa, Oklahoma</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2300 Fourth National Bank Building, Tulsa, OK</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Lessor address</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>OGL 340/302 / Image 1522</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1977-10-14</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Gertrude LaFortune</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2300 Fourth National Building, Tulsa, Oklahoma 74119</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2300 Fourth National Building, Tulsa, OK 74119</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Lessor address</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>OGL 340/304 / Image 1524</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1977-10-14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>George T. Harrison Jr.; Renata Harrison</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>201 North Charles Street, Baltimore, Maryland 21201</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>201 North Charles Street, Baltimore, MD 21201</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lessor address</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>OGL 340/323 / Image 1526</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1977-09-29</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Carol Seidenbach Leach</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>c/o Mrs. J. Leslie Seidenbach, 2827 South Birmingham Place, Tulsa, Oklahoma</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>c/o Mrs. J. Leslie Seidenbach, 2827 South Birmingham Place, Tulsa, OK</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Lessor address</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>OGL 342/564 / Image 1542</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1977-09-29</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Cynthia Seidenbach Kruse</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>c/o M. B. Johnson, 1623 S. College, Tulsa, Oklahoma 74104</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>c/o M. B. Johnson, 1623 S. College, Tulsa, OK 74104</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Lessor address</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>OGL 342/566 / Image 1544</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1977-11-01</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>F.L. Randel</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>P. O. Box 7, c/o Ramada Inn, Big Spring, Texas 79720</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>P.O. Box 7, c/o Ramada Inn, Big Spring, TX 79720</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Lessor address</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>OGL 352/719 / Image 1552</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1978-05-16</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>J.L. Randel</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Box 2609, Wichita Falls, Texas</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>P.O. Box 2609, Wichita Falls, TX</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Lessor address</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>OGL 352/721 / Image 1554</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1978-05-16</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Great Western Oil &amp; Gas, Inc.</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>4010 Palos Verdes Drive North, Suite 206, Rolling Hills Estates, California 90274</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4010 Palos Verdes Drive N, Suite 206, Rolling Hills Estates, CA 90274</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Lessor corporate address</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>OGL 376/369 / Image 1569</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1979-03-21</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Union Oil Company of California</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>P. O. Box 3100, Midland, Texas 79702</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>P.O. Box 3100, Midland, TX 79702</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Assignor address</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Bk 872/Pg 279 / Image 4388</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1985-10-29</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Leede Exploration</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>600 North Marienfeld, Midland, Texas 79701</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>600 N Marienfeld, Midland, TX 79701</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Assignee address</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Bk 872/Pg 279 / Image 4388</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1985-10-29</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Consolidation of Leede Trusts</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>600 North Marienfeld, Midland, Texas 79701</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>600 N Marienfeld, Midland, TX 79701</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Assignor address</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Bk 1014/Pg 75 / Image 4893</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1988-02-18</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Historical only; not a current mailing address</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>